--- a/Simulation_studies/lhc_parameter_comparison_Xdim3.xlsx
+++ b/Simulation_studies/lhc_parameter_comparison_Xdim3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7631550761757844</v>
+        <v>0.9993255646692695</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7900528276994305</v>
+        <v>1.798864739704409</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02689775152364615</v>
+        <v>0.7995391750351392</v>
       </c>
       <c r="E2" t="n">
-        <v>3.404551009831863</v>
+        <v>44.44687570931655</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5894451031379258</v>
+        <v>0.1890207479996102</v>
       </c>
       <c r="C3" t="n">
-        <v>0.686074165927846</v>
+        <v>1.571180154594835</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09662906278992023</v>
+        <v>1.382159406595224</v>
       </c>
       <c r="E3" t="n">
-        <v>14.08434650199067</v>
+        <v>87.96950512346856</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6798174308788012</v>
+        <v>0.7761423167500332</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4766352014548003</v>
+        <v>1.935695394498707</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2031822294240009</v>
+        <v>1.159553077748673</v>
       </c>
       <c r="E4" t="n">
-        <v>42.62845648073033</v>
+        <v>59.90369564571737</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2595668725985254</v>
+        <v>0.05721557649179643</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3161869556386943</v>
+        <v>0.2134515799796908</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05662008304016886</v>
+        <v>0.1562360034878943</v>
       </c>
       <c r="E5" t="n">
-        <v>17.90715335672115</v>
+        <v>73.19505599478799</v>
       </c>
     </row>
     <row r="6">
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09943426950185741</v>
+        <v>0.02055885673838875</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1025961594387158</v>
+        <v>0.005394216754002645</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003161889936858439</v>
+        <v>0.01516463998438611</v>
       </c>
       <c r="E6" t="n">
-        <v>3.081879433067027</v>
+        <v>281.1277461761907</v>
       </c>
     </row>
     <row r="7">
@@ -557,16 +557,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0732625603989468</v>
+        <v>0.1078158329964975</v>
       </c>
       <c r="C7" t="n">
-        <v>0.09393076669245126</v>
+        <v>0.8157776088502947</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02066820629350447</v>
+        <v>0.7079617758537973</v>
       </c>
       <c r="E7" t="n">
-        <v>22.00365973928057</v>
+        <v>86.78367341456622</v>
       </c>
     </row>
     <row r="8">
@@ -576,206 +576,149 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3712906941439512</v>
+        <v>0.06094117622819117</v>
       </c>
       <c r="C8" t="n">
-        <v>0.317617585405287</v>
+        <v>0.1365173232810574</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05367310873866421</v>
+        <v>0.07557614705286619</v>
       </c>
       <c r="E8" t="n">
-        <v>16.89865775856716</v>
+        <v>55.3601149190953</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kappa_p1</t>
+          <t>lambda1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9619300187141491</v>
+        <v>-0.1096186532846115</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8243798073033624</v>
+        <v>-0.4340386057102026</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1375502114107867</v>
+        <v>0.3244199524255911</v>
       </c>
       <c r="E9" t="n">
-        <v>16.68529604827764</v>
+        <v>-74.74449234642475</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kappa_p2</t>
+          <t>lambda2</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8219324184197727</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6885519867075762</v>
+        <v>-0.8160523067543519</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1333804317121965</v>
+        <v>0.8160523067543519</v>
       </c>
       <c r="E10" t="n">
-        <v>19.37114906166734</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kappa_p3</t>
+          <t>lambda3</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7427024598252021</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8983691202088508</v>
+        <v>-0.05517759843365022</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1556666603836487</v>
+        <v>0.05517759843365022</v>
       </c>
       <c r="E11" t="n">
-        <v>17.32769491759241</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>theta_p1</t>
+          <t>sigma1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4275460149770522</v>
+        <v>0.9094950006303357</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4950780853106163</v>
+        <v>0.8030331998483334</v>
       </c>
       <c r="D12" t="n">
-        <v>0.06753207033356412</v>
+        <v>0.1064618007820023</v>
       </c>
       <c r="E12" t="n">
-        <v>13.64069069855797</v>
+        <v>13.25745944278635</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>theta_p2</t>
+          <t>sigma2</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3166162639118174</v>
+        <v>0.4714876912223054</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1338032340902205</v>
+        <v>1.269707644599825</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1828130298215969</v>
+        <v>0.7982199533775198</v>
       </c>
       <c r="E13" t="n">
-        <v>136.6282594472494</v>
+        <v>62.86643675592703</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>theta_p3</t>
+          <t>sigma3</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4888607046247458</v>
+        <v>0.3415208507118044</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1227343068533322</v>
+        <v>0.6169782123930989</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3661263977714136</v>
+        <v>0.2754573616812945</v>
       </c>
       <c r="E14" t="n">
-        <v>298.308115439097</v>
+        <v>44.64620567602649</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sigma1</t>
+          <t>sigma_err</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5788748149422905</v>
+        <v>9.191962403186588e-05</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6903973491353032</v>
+        <v>1.295024085410797e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1115225341930126</v>
+        <v>7.896938317775791e-05</v>
       </c>
       <c r="E15" t="n">
-        <v>16.15338389301326</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>sigma2</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.3218762677519547</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.5019982995677392</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.1801220318157845</v>
-      </c>
-      <c r="E16" t="n">
-        <v>35.88100437210326</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>sigma3</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.126678604324424</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.268229697987273</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.1415510936628491</v>
-      </c>
-      <c r="E17" t="n">
-        <v>52.77234203558078</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>sigma_err</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.001087367436597431</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.001099174847943586</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1.180741134615567e-05</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1.074206835085956</v>
+        <v>609.7908453394354</v>
       </c>
     </row>
   </sheetData>

--- a/Simulation_studies/lhc_parameter_comparison_Xdim3.xlsx
+++ b/Simulation_studies/lhc_parameter_comparison_Xdim3.xlsx
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9993255646692695</v>
+        <v>0.3427434720106656</v>
       </c>
       <c r="C2" t="n">
-        <v>1.798864739704409</v>
+        <v>0.3797711751067785</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7995391750351392</v>
+        <v>0.03702770309611297</v>
       </c>
       <c r="E2" t="n">
-        <v>44.44687570931655</v>
+        <v>9.750003560881645</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1890207479996102</v>
+        <v>0.8585255041900552</v>
       </c>
       <c r="C3" t="n">
-        <v>1.571180154594835</v>
+        <v>0.6393912752292336</v>
       </c>
       <c r="D3" t="n">
-        <v>1.382159406595224</v>
+        <v>0.2191342289608217</v>
       </c>
       <c r="E3" t="n">
-        <v>87.96950512346856</v>
+        <v>34.27232079171834</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7761423167500332</v>
+        <v>0.5152300132846954</v>
       </c>
       <c r="C4" t="n">
-        <v>1.935695394498707</v>
+        <v>0.6459660980904713</v>
       </c>
       <c r="D4" t="n">
-        <v>1.159553077748673</v>
+        <v>0.1307360848057759</v>
       </c>
       <c r="E4" t="n">
-        <v>59.90369564571737</v>
+        <v>20.23884615496734</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05721557649179643</v>
+        <v>0.4515490512955448</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2134515799796908</v>
+        <v>0.4075322176764574</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1562360034878943</v>
+        <v>0.04401683361908737</v>
       </c>
       <c r="E5" t="n">
-        <v>73.19505599478799</v>
+        <v>10.80082302941571</v>
       </c>
     </row>
     <row r="6">
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02055885673838875</v>
+        <v>0.2385725489543128</v>
       </c>
       <c r="C6" t="n">
-        <v>0.005394216754002645</v>
+        <v>0.4686158218945422</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01516463998438611</v>
+        <v>0.2300432729402294</v>
       </c>
       <c r="E6" t="n">
-        <v>281.1277461761907</v>
+        <v>49.08995005977381</v>
       </c>
     </row>
     <row r="7">
@@ -557,16 +557,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1078158329964975</v>
+        <v>0.4335810400477508</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8157776088502947</v>
+        <v>0.114264358772</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7079617758537973</v>
+        <v>0.3193166812757507</v>
       </c>
       <c r="E7" t="n">
-        <v>86.78367341456622</v>
+        <v>279.4543151578057</v>
       </c>
     </row>
     <row r="8">
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06094117622819117</v>
+        <v>0.09112060806717054</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1365173232810574</v>
+        <v>0.1916306962062198</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07557614705286619</v>
+        <v>0.1005100881390493</v>
       </c>
       <c r="E8" t="n">
-        <v>55.3601149190953</v>
+        <v>52.44988935952475</v>
       </c>
     </row>
     <row r="9">
@@ -595,16 +595,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.1096186532846115</v>
+        <v>-0.3570421240820807</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.4340386057102026</v>
+        <v>-0.7232694414487358</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3244199524255911</v>
+        <v>0.3662273173666551</v>
       </c>
       <c r="E9" t="n">
-        <v>-74.74449234642475</v>
+        <v>-50.63497728219902</v>
       </c>
     </row>
     <row r="10">
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.2953079111133299</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.8160523067543519</v>
+        <v>-0.7301239977019793</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8160523067543519</v>
+        <v>1.025431908815309</v>
       </c>
       <c r="E10" t="n">
-        <v>-100</v>
+        <v>-140.4462683109709</v>
       </c>
     </row>
     <row r="11">
@@ -633,16 +633,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>-0.1987244721788768</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.05517759843365022</v>
+        <v>-0.740341924454755</v>
       </c>
       <c r="D11" t="n">
-        <v>0.05517759843365022</v>
+        <v>0.5416174522758782</v>
       </c>
       <c r="E11" t="n">
-        <v>-100</v>
+        <v>-73.15774433208915</v>
       </c>
     </row>
     <row r="12">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9094950006303357</v>
+        <v>0.0656652285416946</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8030331998483334</v>
+        <v>0.03502933857832953</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1064618007820023</v>
+        <v>0.03063588996336507</v>
       </c>
       <c r="E12" t="n">
-        <v>13.25745944278635</v>
+        <v>87.45780310655819</v>
       </c>
     </row>
     <row r="13">
@@ -671,16 +671,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4714876912223054</v>
+        <v>0.3531725841499661</v>
       </c>
       <c r="C13" t="n">
-        <v>1.269707644599825</v>
+        <v>0.1763969430417633</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7982199533775198</v>
+        <v>0.1767756411082028</v>
       </c>
       <c r="E13" t="n">
-        <v>62.86643675592703</v>
+        <v>100.2146851639883</v>
       </c>
     </row>
     <row r="14">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3415208507118044</v>
+        <v>0.4407562571692937</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6169782123930989</v>
+        <v>0.2884150310257947</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2754573616812945</v>
+        <v>0.152341226143499</v>
       </c>
       <c r="E14" t="n">
-        <v>44.64620567602649</v>
+        <v>52.82014103137163</v>
       </c>
     </row>
     <row r="15">
@@ -709,16 +709,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.191962403186588e-05</v>
+        <v>2.553540405143308e-05</v>
       </c>
       <c r="C15" t="n">
-        <v>1.295024085410797e-05</v>
+        <v>2.38691435613185e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>7.896938317775791e-05</v>
+        <v>1.666260490114573e-06</v>
       </c>
       <c r="E15" t="n">
-        <v>609.7908453394354</v>
+        <v>6.980813894030351</v>
       </c>
     </row>
   </sheetData>

--- a/Simulation_studies/lhc_parameter_comparison_Xdim3.xlsx
+++ b/Simulation_studies/lhc_parameter_comparison_Xdim3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,263 +462,607 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3427434720106656</v>
+        <v>1.648143084474868</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3797711751067785</v>
+        <v>1.497869415359124</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03702770309611297</v>
+        <v>0.1502736691157442</v>
       </c>
       <c r="E2" t="n">
-        <v>9.750003560881645</v>
+        <v>10.03249466040504</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>kappa2</t>
+          <t xml:space="preserve">  ↳ SE(kappa1)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8585255041900552</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.6393912752292336</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.2191342289608217</v>
-      </c>
-      <c r="E3" t="n">
-        <v>34.27232079171834</v>
+        <v>0.0001573081792131326</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kappa3</t>
+          <t>kappa2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5152300132846954</v>
+        <v>1.583764270828442</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6459660980904713</v>
+        <v>1.024520756929915</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1307360848057759</v>
+        <v>0.5592435138985277</v>
       </c>
       <c r="E4" t="n">
-        <v>20.23884615496734</v>
+        <v>54.58586467045922</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>theta1</t>
+          <t xml:space="preserve">  ↳ SE(kappa2)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4515490512955448</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.4075322176764574</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.04401683361908737</v>
-      </c>
-      <c r="E5" t="n">
-        <v>10.80082302941571</v>
+        <v>2.34422103877054e-05</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>theta2</t>
+          <t>kappa3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2385725489543128</v>
+        <v>0.8408170184401641</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4686158218945422</v>
+        <v>0.8403708700586656</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2300432729402294</v>
+        <v>0.000446148381498479</v>
       </c>
       <c r="E6" t="n">
-        <v>49.08995005977381</v>
+        <v>0.05308946292573585</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>theta3</t>
+          <t xml:space="preserve">  ↳ SE(kappa3)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4335810400477508</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.114264358772</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.3193166812757507</v>
-      </c>
-      <c r="E7" t="n">
-        <v>279.4543151578057</v>
+        <v>0.000361285560455075</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gamma1</t>
+          <t>theta1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.09112060806717054</v>
+        <v>0.2252730796434458</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1916306962062198</v>
+        <v>0.1362189365177941</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1005100881390493</v>
+        <v>0.08905414312565177</v>
       </c>
       <c r="E8" t="n">
-        <v>52.44988935952475</v>
+        <v>65.37574393264975</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>lambda1</t>
+          <t xml:space="preserve">  ↳ SE(theta1)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.3570421240820807</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.7232694414487358</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.3662273173666551</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-50.63497728219902</v>
+        <v>1.730728457222539</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>lambda2</t>
+          <t>theta2</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2953079111133299</v>
+        <v>0.4070387171964926</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.7301239977019793</v>
+        <v>0.5239102534017285</v>
       </c>
       <c r="D10" t="n">
-        <v>1.025431908815309</v>
+        <v>0.1168715362052358</v>
       </c>
       <c r="E10" t="n">
-        <v>-140.4462683109709</v>
+        <v>22.30754894495643</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>lambda3</t>
+          <t xml:space="preserve">  ↳ SE(theta2)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1987244721788768</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.740341924454755</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.5416174522758782</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-73.15774433208915</v>
+        <v>1.188446095593312</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sigma1</t>
+          <t>theta3</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0656652285416946</v>
+        <v>0.5231535233115756</v>
       </c>
       <c r="C12" t="n">
-        <v>0.03502933857832953</v>
+        <v>0.9856181305003979</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03063588996336507</v>
+        <v>0.4624646071888223</v>
       </c>
       <c r="E12" t="n">
-        <v>87.45780310655819</v>
+        <v>46.92127639271705</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sigma2</t>
+          <t xml:space="preserve">  ↳ SE(theta3)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3531725841499661</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.1763969430417633</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.1767756411082028</v>
-      </c>
-      <c r="E13" t="n">
-        <v>100.2146851639883</v>
+        <v>0.1017005395040504</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sigma3</t>
+          <t>gamma1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4407562571692937</v>
+        <v>0.01041042826246162</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2884150310257947</v>
+        <v>0.007098252906902286</v>
       </c>
       <c r="D14" t="n">
-        <v>0.152341226143499</v>
+        <v>0.00331217535555933</v>
       </c>
       <c r="E14" t="n">
-        <v>52.82014103137163</v>
+        <v>46.66183917367323</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t xml:space="preserve">  ↳ SE(gamma1)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>lambda1</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ SE(lambda1)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.2362617502815444</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>lambda2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ SE(lambda2)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.305723859909957</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>lambda3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ SE(lambda3)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.06318094925928019</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sigma1</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.5972760897564182</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.6729288386242396</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.07565274886782136</v>
+      </c>
+      <c r="E22" t="n">
+        <v>11.24231040870363</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ SE(sigma1)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.02631584990974017</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sigma2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.4680299270258637</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.4628867259900097</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.005143201035853973</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.111114393019984</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ SE(sigma2)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.04573133800587516</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sigma3</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.1431753219612945</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.06468520120687075</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0784901207544237</v>
+      </c>
+      <c r="E26" t="n">
+        <v>121.3416968487169</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ SE(sigma3)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.03298756061780878</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>sigma_err</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>2.553540405143308e-05</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2.38691435613185e-05</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.666260490114573e-06</v>
-      </c>
-      <c r="E15" t="n">
-        <v>6.980813894030351</v>
+      <c r="B28" t="n">
+        <v>1.155319057468936e-05</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.255929524729636e-05</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.006104672607001e-06</v>
+      </c>
+      <c r="E28" t="n">
+        <v>8.010837015903302</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ SE(sigma_err)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1.499296818518495e-07</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Simulation_studies/lhc_parameter_comparison_Xdim3.xlsx
+++ b/Simulation_studies/lhc_parameter_comparison_Xdim3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,17 +441,42 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LogLike</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Filipovic</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Abs Error, Kalman</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Rel Error (%), Kalman</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Abs Error, Filipovic</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Rel Error (%), Filipovic</t>
         </is>
       </c>
     </row>
@@ -462,607 +487,473 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.648143084474868</v>
+        <v>0.6025547307883151</v>
       </c>
       <c r="C2" t="n">
-        <v>1.497869415359124</v>
+        <v>0.2429192386014033</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1502736691157442</v>
+        <v>7760.085940288875</v>
       </c>
       <c r="E2" t="n">
-        <v>10.03249466040504</v>
+        <v>0.6845285639916602</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.7490602403257222</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.146505509537407</v>
+      </c>
+      <c r="H2" t="n">
+        <v>19.55857508518947</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.06453167633406198</v>
+      </c>
+      <c r="J2" t="n">
+        <v>8.615018240188661</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ SE(kappa1)</t>
+          <t>kappa2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001573081792131326</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.7925516226357185</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.002462554559647975</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.3520047834001978</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5882238779386133</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2043277446971052</v>
+      </c>
+      <c r="H3" t="n">
+        <v>34.73639074516264</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2362190945384155</v>
+      </c>
+      <c r="J3" t="n">
+        <v>40.15802543858432</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kappa2</t>
+          <t>kappa3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.583764270828442</v>
+        <v>0.3956893854724085</v>
       </c>
       <c r="C4" t="n">
-        <v>1.024520756929915</v>
+        <v>0.01029549799012986</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5592435138985277</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>54.58586467045922</v>
+        <v>0.224451294552636</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2633832220044289</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1323061634679796</v>
+      </c>
+      <c r="H4" t="n">
+        <v>50.23333014953961</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.03893192745179291</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14.78147588730548</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ SE(kappa2)</t>
+          <t>theta1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.34422103877054e-05</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3839778716799071</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.6615857128906379</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2624446691395957</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3114920179524447</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.07248585372746236</v>
+      </c>
+      <c r="H5" t="n">
+        <v>23.27053328812064</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.04904734881284906</v>
+      </c>
+      <c r="J5" t="n">
+        <v>15.74594082225795</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>kappa3</t>
+          <t>theta2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8408170184401641</v>
+        <v>0.2709045569694274</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8403708700586656</v>
+        <v>0.5326262866364538</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000446148381498479</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05308946292573585</v>
+        <v>0.6272113698761134</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.381705172732845</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1108006157634175</v>
+      </c>
+      <c r="H6" t="n">
+        <v>29.02780042778376</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2455061971432684</v>
+      </c>
+      <c r="J6" t="n">
+        <v>64.31827878714599</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ SE(kappa3)</t>
+          <t>theta3</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.000361285560455075</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3500509303218127</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.01748379852446771</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.4153615388926307</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4027361115897557</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05268518126794303</v>
+      </c>
+      <c r="H7" t="n">
+        <v>13.08181207291647</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.01262542730287503</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.134913145244802</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>theta1</t>
+          <t>gamma1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2252730796434458</v>
+        <v>0.1919889358399536</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1362189365177941</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08905414312565177</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>65.37574393264975</v>
+        <v>0.1312223345697978</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1557460089762224</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.03624292686373118</v>
+      </c>
+      <c r="H8" t="n">
+        <v>23.27053328812064</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.02452367440642453</v>
+      </c>
+      <c r="J8" t="n">
+        <v>15.74594082225795</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ SE(theta1)</t>
+          <t>lambda1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.730728457222539</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.8200581589841317</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1787057619283544</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.4295140081993604</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.3905441507847713</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-90.92698802119138</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.4295140081993604</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-99.99999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>theta2</t>
+          <t>lambda2</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4070387171964926</v>
+        <v>0.01012226912353542</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5239102534017285</v>
+        <v>0.1846807361735553</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1168715362052358</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>22.30754894495643</v>
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.4297213724629754</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.4398436415865108</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-102.3555423984427</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.4297213724629754</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-100</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ SE(theta2)</t>
+          <t>lambda3</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.188446095593312</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.7946002693749923</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.005114031618909441</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.3513482699482423</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.44325199942675</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-126.1574447177572</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.3513482699482423</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-100</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>theta3</t>
+          <t>sigma1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5231535233115756</v>
+        <v>0.03051966036966669</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9856181305003979</v>
+        <v>0.004195893388278475</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4624646071888223</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>46.92127639271705</v>
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.02412886300876088</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.006390797360905809</v>
+      </c>
+      <c r="H12" t="n">
+        <v>26.4861106741142</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.02412886300876088</v>
+      </c>
+      <c r="J12" t="n">
+        <v>99.99999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ SE(theta3)</t>
+          <t>sigma2</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1017005395040504</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.5200312263671123</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.01889098680729684</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.5719083712717069</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05187714490459461</v>
+      </c>
+      <c r="H13" t="n">
+        <v>9.070883993049367</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5719083712717069</v>
+      </c>
+      <c r="J13" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gamma1</t>
+          <t>sigma3</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01041042826246162</v>
+        <v>0.003344301537598737</v>
       </c>
       <c r="C14" t="n">
-        <v>0.007098252906902286</v>
+        <v>0.01531640438134382</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00331217535555933</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>46.66183917367323</v>
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.006154907563359367</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.00281060602576063</v>
+      </c>
+      <c r="H14" t="n">
+        <v>45.6644717540907</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.006154907563359367</v>
+      </c>
+      <c r="J14" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ SE(gamma1)</t>
+          <t>sigma_err</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>lambda1</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ↳ SE(lambda1)</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.2362617502815444</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>lambda2</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ↳ SE(lambda2)</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.305723859909957</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>lambda3</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ↳ SE(lambda3)</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.06318094925928019</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>sigma1</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0.5972760897564182</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.6729288386242396</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.07565274886782136</v>
-      </c>
-      <c r="E22" t="n">
-        <v>11.24231040870363</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ↳ SE(sigma1)</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0.02631584990974017</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>sigma2</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0.4680299270258637</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.4628867259900097</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.005143201035853973</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1.111114393019984</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ↳ SE(sigma2)</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>0.04573133800587516</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>sigma3</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0.1431753219612945</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.06468520120687075</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.0784901207544237</v>
-      </c>
-      <c r="E26" t="n">
-        <v>121.3416968487169</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ↳ SE(sigma3)</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0.03298756061780878</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>sigma_err</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1.155319057468936e-05</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1.255929524729636e-05</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1.006104672607001e-06</v>
-      </c>
-      <c r="E28" t="n">
-        <v>8.010837015903302</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ↳ SE(sigma_err)</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>1.499296818518495e-07</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.042697756073048e-05</v>
+      </c>
+      <c r="C15" t="n">
+        <v>9.037557003378965e-07</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>8.0870820885638e-05</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.438433249075288e-07</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.5488299983193959</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8.0870820885638e-05</v>
+      </c>
+      <c r="J15" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Simulation_studies/lhc_parameter_comparison_Xdim3.xlsx
+++ b/Simulation_studies/lhc_parameter_comparison_Xdim3.xlsx
@@ -487,31 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6025547307883151</v>
+        <v>0.4567993872095492</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2429192386014033</v>
+        <v>0.01659463745605039</v>
       </c>
       <c r="D2" t="n">
-        <v>7760.085940288875</v>
+        <v>42318.76074072206</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6845285639916602</v>
+        <v>0.4633667210801545</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7490602403257222</v>
+        <v>0.4548840732360043</v>
       </c>
       <c r="G2" t="n">
-        <v>0.146505509537407</v>
+        <v>0.001915313973544885</v>
       </c>
       <c r="H2" t="n">
-        <v>19.55857508518947</v>
+        <v>0.4210554042746572</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06453167633406198</v>
+        <v>0.00848264784415026</v>
       </c>
       <c r="J2" t="n">
-        <v>8.615018240188661</v>
+        <v>1.86479332718894</v>
       </c>
     </row>
     <row r="3">
@@ -521,31 +521,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7925516226357185</v>
+        <v>1.134632634600112</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002462554559647975</v>
+        <v>0.01926752164005136</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3520047834001978</v>
+        <v>0.9548804354301577</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5882238779386133</v>
+        <v>0.9288508912314156</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2043277446971052</v>
+        <v>0.205781743368696</v>
       </c>
       <c r="H3" t="n">
-        <v>34.73639074516264</v>
+        <v>22.15444322779114</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2362190945384155</v>
+        <v>0.02602954419874204</v>
       </c>
       <c r="J3" t="n">
-        <v>40.15802543858432</v>
+        <v>2.802338291804146</v>
       </c>
     </row>
     <row r="4">
@@ -555,31 +555,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3956893854724085</v>
+        <v>0.3686239075691162</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01029549799012986</v>
+        <v>0.1380791334933814</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.224451294552636</v>
+        <v>0.3765848801969003</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2633832220044289</v>
+        <v>0.4000454185883696</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1323061634679796</v>
+        <v>0.03142151101925339</v>
       </c>
       <c r="H4" t="n">
-        <v>50.23333014953961</v>
+        <v>7.854485905657837</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03893192745179291</v>
+        <v>0.02346053839146933</v>
       </c>
       <c r="J4" t="n">
-        <v>14.78147588730548</v>
+        <v>5.864468708141679</v>
       </c>
     </row>
     <row r="5">
@@ -589,31 +589,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3839778716799071</v>
+        <v>0.09704596451060918</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6615857128906379</v>
+        <v>0.8833207348538523</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2624446691395957</v>
+        <v>0.1416440683429512</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3114920179524447</v>
+        <v>0.143232061158843</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07248585372746236</v>
+        <v>0.04618609664823378</v>
       </c>
       <c r="H5" t="n">
-        <v>23.27053328812064</v>
+        <v>32.24564128628565</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04904734881284906</v>
+        <v>0.001587992815891726</v>
       </c>
       <c r="J5" t="n">
-        <v>15.74594082225795</v>
+        <v>1.108685306239262</v>
       </c>
     </row>
     <row r="6">
@@ -623,31 +623,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2709045569694274</v>
+        <v>0.2514396179633418</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5326262866364538</v>
+        <v>0.2575314881121541</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6272113698761134</v>
+        <v>0.2274598489923965</v>
       </c>
       <c r="F6" t="n">
-        <v>0.381705172732845</v>
+        <v>0.5686252214032469</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1108006157634175</v>
+        <v>0.3171856034399051</v>
       </c>
       <c r="H6" t="n">
-        <v>29.02780042778376</v>
+        <v>55.78113518376095</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2455061971432684</v>
+        <v>0.3411653724108504</v>
       </c>
       <c r="J6" t="n">
-        <v>64.31827878714599</v>
+        <v>59.99828350366281</v>
       </c>
     </row>
     <row r="7">
@@ -657,31 +657,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3500509303218127</v>
+        <v>0.3088023843012261</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01748379852446771</v>
+        <v>0.2762034928254634</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4153615388926307</v>
+        <v>0.2262625292810097</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4027361115897557</v>
+        <v>0.09087250393580103</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05268518126794303</v>
+        <v>0.217929880365425</v>
       </c>
       <c r="H7" t="n">
-        <v>13.08181207291647</v>
+        <v>239.8193853218644</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01262542730287503</v>
+        <v>0.1353900253452087</v>
       </c>
       <c r="J7" t="n">
-        <v>3.134913145244802</v>
+        <v>148.9889894977012</v>
       </c>
     </row>
     <row r="8">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1919889358399536</v>
+        <v>0.2283996936047746</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -700,22 +700,22 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1312223345697978</v>
+        <v>0.2316833605400773</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1557460089762224</v>
+        <v>0.2274420366180021</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03624292686373118</v>
+        <v>0.0009576569867724427</v>
       </c>
       <c r="H8" t="n">
-        <v>23.27053328812064</v>
+        <v>0.4210554042746572</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02452367440642453</v>
+        <v>0.00424132392207513</v>
       </c>
       <c r="J8" t="n">
-        <v>15.74594082225795</v>
+        <v>1.86479332718894</v>
       </c>
     </row>
     <row r="9">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.8200581589841317</v>
+        <v>-0.04409269786218029</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1787057619283544</v>
+        <v>0.1712862711585168</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -737,19 +737,19 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4295140081993604</v>
+        <v>0.05888265071313081</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3905441507847713</v>
+        <v>0.1029753485753111</v>
       </c>
       <c r="H9" t="n">
-        <v>-90.92698802119138</v>
+        <v>174.882324977173</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4295140081993604</v>
+        <v>0.05888265071313081</v>
       </c>
       <c r="J9" t="n">
-        <v>-99.99999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01012226912353542</v>
+        <v>-0.5790974243810623</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1846807361735553</v>
+        <v>0.03780038521310793</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -771,16 +771,16 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4297213724629754</v>
+        <v>-0.9217664850582918</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4398436415865108</v>
+        <v>0.3426690606772296</v>
       </c>
       <c r="H10" t="n">
-        <v>-102.3555423984427</v>
+        <v>-37.17525709947671</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4297213724629754</v>
+        <v>0.9217664850582918</v>
       </c>
       <c r="J10" t="n">
         <v>-100</v>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.7946002693749923</v>
+        <v>-0.5459893367954994</v>
       </c>
       <c r="C11" t="n">
-        <v>0.005114031618909441</v>
+        <v>0.09329680121820756</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -805,16 +805,16 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3513482699482423</v>
+        <v>-0.07966860741459947</v>
       </c>
       <c r="G11" t="n">
-        <v>0.44325199942675</v>
+        <v>0.4663207293809</v>
       </c>
       <c r="H11" t="n">
-        <v>-126.1574447177572</v>
+        <v>-585.325568644803</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3513482699482423</v>
+        <v>0.07966860741459947</v>
       </c>
       <c r="J11" t="n">
         <v>-100</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03051966036966669</v>
+        <v>0.1973098894946935</v>
       </c>
       <c r="C12" t="n">
-        <v>0.004195893388278475</v>
+        <v>0.005038934150960166</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -839,19 +839,19 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02412886300876088</v>
+        <v>0.2007543722706258</v>
       </c>
       <c r="G12" t="n">
-        <v>0.006390797360905809</v>
+        <v>0.003444482775932262</v>
       </c>
       <c r="H12" t="n">
-        <v>26.4861106741142</v>
+        <v>1.715769742383965</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02412886300876088</v>
+        <v>0.2007543722706258</v>
       </c>
       <c r="J12" t="n">
-        <v>99.99999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5200312263671123</v>
+        <v>0.0931680723491829</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01889098680729684</v>
+        <v>0.02646351968335298</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -873,16 +873,16 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5719083712717069</v>
+        <v>0.006780775943194382</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05187714490459461</v>
+        <v>0.08638729640598851</v>
       </c>
       <c r="H13" t="n">
-        <v>9.070883993049367</v>
+        <v>1274.003110111495</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5719083712717069</v>
+        <v>0.006780775943194382</v>
       </c>
       <c r="J13" t="n">
         <v>100</v>
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.003344301537598737</v>
+        <v>0.1892769921205084</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01531640438134382</v>
+        <v>0.01721536253143845</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -907,16 +907,16 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.006154907563359367</v>
+        <v>0.1169776506168013</v>
       </c>
       <c r="G14" t="n">
-        <v>0.00281060602576063</v>
+        <v>0.07229934150370712</v>
       </c>
       <c r="H14" t="n">
-        <v>45.6644717540907</v>
+        <v>61.80611520447385</v>
       </c>
       <c r="I14" t="n">
-        <v>0.006154907563359367</v>
+        <v>0.1169776506168013</v>
       </c>
       <c r="J14" t="n">
         <v>100</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.042697756073048e-05</v>
+        <v>3.926188110361961e-05</v>
       </c>
       <c r="C15" t="n">
-        <v>9.037557003378965e-07</v>
+        <v>4.174254171671995e-07</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -941,16 +941,16 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>8.0870820885638e-05</v>
+        <v>3.813029473349604e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>4.438433249075288e-07</v>
+        <v>1.131586370123565e-06</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5488299983193959</v>
+        <v>2.96768325037233</v>
       </c>
       <c r="I15" t="n">
-        <v>8.0870820885638e-05</v>
+        <v>3.813029473349604e-05</v>
       </c>
       <c r="J15" t="n">
         <v>100</v>

--- a/Simulation_studies/lhc_parameter_comparison_Xdim3.xlsx
+++ b/Simulation_studies/lhc_parameter_comparison_Xdim3.xlsx
@@ -487,31 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4567993872095492</v>
+        <v>0.4489887673226649</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01659463745605039</v>
+        <v>0.06530833034974454</v>
       </c>
       <c r="D2" t="n">
-        <v>42318.76074072206</v>
+        <v>42875.8266423395</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4633667210801545</v>
+        <v>0.4841506745434334</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4548840732360043</v>
+        <v>0.454611378925467</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001915313973544885</v>
+        <v>0.005622611602802086</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4210554042746572</v>
+        <v>1.236795175715104</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00848264784415026</v>
+        <v>0.02953929561796642</v>
       </c>
       <c r="J2" t="n">
-        <v>1.86479332718894</v>
+        <v>6.497702650511385</v>
       </c>
     </row>
     <row r="3">
@@ -521,31 +521,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.134632634600112</v>
+        <v>0.3222572696769264</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01926752164005136</v>
+        <v>0.1439624075238777</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9548804354301577</v>
+        <v>1.034999212406493</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9288508912314156</v>
+        <v>0.9288383342725333</v>
       </c>
       <c r="G3" t="n">
-        <v>0.205781743368696</v>
+        <v>0.6065810645956069</v>
       </c>
       <c r="H3" t="n">
-        <v>22.15444322779114</v>
+        <v>65.30534348269353</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02602954419874204</v>
+        <v>0.10616087813396</v>
       </c>
       <c r="J3" t="n">
-        <v>2.802338291804146</v>
+        <v>11.4294247143778</v>
       </c>
     </row>
     <row r="4">
@@ -555,31 +555,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3686239075691162</v>
+        <v>1.454657396837872</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1380791334933814</v>
+        <v>0.002806181133066889</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3765848801969003</v>
+        <v>0.3529988050603791</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4000454185883696</v>
+        <v>0.3999395338465856</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03142151101925339</v>
+        <v>1.054717862991286</v>
       </c>
       <c r="H4" t="n">
-        <v>7.854485905657837</v>
+        <v>263.7193309816352</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02346053839146933</v>
+        <v>0.04694072878620659</v>
       </c>
       <c r="J4" t="n">
-        <v>5.864468708141679</v>
+        <v>11.73695641807013</v>
       </c>
     </row>
     <row r="5">
@@ -589,31 +589,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09704596451060918</v>
+        <v>0.1554301070144915</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8833207348538523</v>
+        <v>2.222008643536074</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1416440683429512</v>
+        <v>0.2542569515266721</v>
       </c>
       <c r="F5" t="n">
         <v>0.143232061158843</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04618609664823378</v>
+        <v>0.01219804585564854</v>
       </c>
       <c r="H5" t="n">
-        <v>32.24564128628565</v>
+        <v>8.516281729773496</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001587992815891726</v>
+        <v>0.1110248903678291</v>
       </c>
       <c r="J5" t="n">
-        <v>1.108685306239262</v>
+        <v>77.5139933542558</v>
       </c>
     </row>
     <row r="6">
@@ -623,31 +623,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2514396179633418</v>
+        <v>0.2474317757041427</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2575314881121541</v>
+        <v>0.3399026940603611</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2274598489923965</v>
+        <v>0.363783369547438</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5686252214032469</v>
+        <v>0.568733265488213</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3171856034399051</v>
+        <v>0.3213014897840704</v>
       </c>
       <c r="H6" t="n">
-        <v>55.78113518376095</v>
+        <v>56.49423188008146</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3411653724108504</v>
+        <v>0.2049498959407751</v>
       </c>
       <c r="J6" t="n">
-        <v>59.99828350366281</v>
+        <v>36.03620684379023</v>
       </c>
     </row>
     <row r="7">
@@ -657,31 +657,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3088023843012261</v>
+        <v>0.2019480633064334</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2762034928254634</v>
+        <v>0.352024126689253</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2262625292810097</v>
+        <v>0.07548952047834601</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09087250393580103</v>
+        <v>0.09091260474779433</v>
       </c>
       <c r="G7" t="n">
-        <v>0.217929880365425</v>
+        <v>0.1110354585586391</v>
       </c>
       <c r="H7" t="n">
-        <v>239.8193853218644</v>
+        <v>122.1342836526009</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1353900253452087</v>
+        <v>0.01542308426944833</v>
       </c>
       <c r="J7" t="n">
-        <v>148.9889894977012</v>
+        <v>16.96473697155016</v>
       </c>
     </row>
     <row r="8">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2283996936047746</v>
+        <v>0.2244943836613325</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -700,22 +700,22 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2316833605400773</v>
+        <v>0.2420753372717167</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2274420366180021</v>
+        <v>0.2273056894627335</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009576569867724427</v>
+        <v>0.002811305801401043</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4210554042746572</v>
+        <v>1.236795175715104</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00424132392207513</v>
+        <v>0.01476964780898321</v>
       </c>
       <c r="J8" t="n">
-        <v>1.86479332718894</v>
+        <v>6.497702650511385</v>
       </c>
     </row>
     <row r="9">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.04409269786218029</v>
+        <v>-0.04165241344635617</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1712862711585168</v>
+        <v>0.7048834845622669</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -737,16 +737,16 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05888265071313081</v>
+        <v>0.0943808593469333</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1029753485753111</v>
+        <v>0.1360332727932895</v>
       </c>
       <c r="H9" t="n">
-        <v>174.882324977173</v>
+        <v>144.1322676383425</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05888265071313081</v>
+        <v>0.0943808593469333</v>
       </c>
       <c r="J9" t="n">
         <v>100</v>
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.5790974243810623</v>
+        <v>-0.3970908163613869</v>
       </c>
       <c r="C10" t="n">
-        <v>0.03780038521310793</v>
+        <v>0.117024612235506</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -771,16 +771,16 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9217664850582918</v>
+        <v>-0.5484370659843639</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3426690606772296</v>
+        <v>0.151346249622977</v>
       </c>
       <c r="H10" t="n">
-        <v>-37.17525709947671</v>
+        <v>-27.59591920566724</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9217664850582918</v>
+        <v>0.5484370659843639</v>
       </c>
       <c r="J10" t="n">
         <v>-100</v>
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.5459893367954994</v>
+        <v>-0.0892479363055457</v>
       </c>
       <c r="C11" t="n">
-        <v>0.09329680121820756</v>
+        <v>0.04606279336428746</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -805,16 +805,16 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.07966860741459947</v>
+        <v>-0.003638107319686945</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4663207293809</v>
+        <v>0.08560982898585875</v>
       </c>
       <c r="H11" t="n">
-        <v>-585.325568644803</v>
+        <v>-2353.141935164941</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07966860741459947</v>
+        <v>0.003638107319686945</v>
       </c>
       <c r="J11" t="n">
         <v>-100</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1973098894946935</v>
+        <v>0.1593040570106229</v>
       </c>
       <c r="C12" t="n">
-        <v>0.005038934150960166</v>
+        <v>0.005040936530105459</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -839,16 +839,16 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2007543722706258</v>
+        <v>0.1625698356954289</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003444482775932262</v>
+        <v>0.003265778684806042</v>
       </c>
       <c r="H12" t="n">
-        <v>1.715769742383965</v>
+        <v>2.008846641713047</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2007543722706258</v>
+        <v>0.1625698356954289</v>
       </c>
       <c r="J12" t="n">
         <v>100</v>
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0931680723491829</v>
+        <v>0.01009147919495246</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02646351968335298</v>
+        <v>0.03353455544948418</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -873,16 +873,16 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.006780775943194382</v>
+        <v>0.006781374279348609</v>
       </c>
       <c r="G13" t="n">
-        <v>0.08638729640598851</v>
+        <v>0.003310104915603848</v>
       </c>
       <c r="H13" t="n">
-        <v>1274.003110111495</v>
+        <v>48.81171248258846</v>
       </c>
       <c r="I13" t="n">
-        <v>0.006780775943194382</v>
+        <v>0.006781374279348609</v>
       </c>
       <c r="J13" t="n">
         <v>100</v>
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1892769921205084</v>
+        <v>0.5183885680167379</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01721536253143845</v>
+        <v>0.06221877956406072</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -907,19 +907,19 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1169776506168013</v>
+        <v>0.1169879727330586</v>
       </c>
       <c r="G14" t="n">
-        <v>0.07229934150370712</v>
+        <v>0.4014005952836793</v>
       </c>
       <c r="H14" t="n">
-        <v>61.80611520447385</v>
+        <v>343.1127028755249</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1169776506168013</v>
+        <v>0.1169879727330586</v>
       </c>
       <c r="J14" t="n">
-        <v>100</v>
+        <v>99.99999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.926188110361961e-05</v>
+        <v>3.764560864146383e-05</v>
       </c>
       <c r="C15" t="n">
-        <v>4.174254171671995e-07</v>
+        <v>4.128377890067342e-07</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -944,10 +944,10 @@
         <v>3.813029473349604e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>1.131586370123565e-06</v>
+        <v>4.846860920322107e-07</v>
       </c>
       <c r="H15" t="n">
-        <v>2.96768325037233</v>
+        <v>1.271131249888903</v>
       </c>
       <c r="I15" t="n">
         <v>3.813029473349604e-05</v>
